--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486393_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486393_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3654</v>
+        <v>6.3175</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1499</v>
+        <v>10.2869</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.7845</v>
+        <v>-3.9694</v>
       </c>
       <c r="G2" t="n">
         <v>7.4845</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3769</v>
+        <v>-0.4248</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2824</v>
+        <v>-0.1454</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0945</v>
+        <v>-0.2794</v>
       </c>
       <c r="V2" t="n">
         <v>2.0854</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>S. LLORENTE PAZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3402</v>
+        <v>0.0127</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6869</v>
+        <v>-0.5528</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3467</v>
+        <v>0.5654</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.6993</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.2626</v>
+        <v>-0.5292</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4367</v>
+        <v>-0.4088</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4999</v>
+        <v>-0.6886</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.6147</v>
+        <v>0.0182</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1147</v>
+        <v>-0.7068</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1994</v>
+        <v>-0.2495</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6479</v>
+        <v>-0.5475</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5514</v>
+        <v>0.298</v>
       </c>
       <c r="P3" t="n">
         <v>0.2175</v>
@@ -688,28 +688,28 @@
         <v>0.2175</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9318</v>
+        <v>0.1067</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2966</v>
+        <v>0.1358</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3648</v>
+        <v>-0.0291</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8902</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LLORENTE PAZ</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3171</v>
+        <v>-0.2936</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2175</v>
+        <v>0.9298</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5346</v>
+        <v>-1.2234</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-2.6993</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5292</v>
+        <v>-2.2626</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4088</v>
+        <v>-0.4367</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6886</v>
+        <v>-1.4999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0182</v>
+        <v>-1.6147</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7068</v>
+        <v>0.1147</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2495</v>
+        <v>-1.1994</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5475</v>
+        <v>-0.6479</v>
       </c>
       <c r="O4" t="n">
-        <v>0.298</v>
+        <v>-0.5514</v>
       </c>
       <c r="P4" t="n">
         <v>0.2175</v>
@@ -766,22 +766,22 @@
         <v>0.2175</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4111</v>
+        <v>0.298</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4711</v>
+        <v>0.5396</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.06</v>
+        <v>-0.2415</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6264999999999999</v>
+        <v>1.8902</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6264999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.3064</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4614</v>
+        <v>0.1946</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4702</v>
+        <v>-0.501</v>
       </c>
       <c r="G5" t="n">
         <v>-4.3121</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.214</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0853</v>
+        <v>-0.3521</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1287</v>
+        <v>-0.1595</v>
       </c>
       <c r="V5" t="n">
         <v>2.3422</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4153</v>
+        <v>-0.3228</v>
       </c>
       <c r="E6" t="n">
         <v>0.552</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.8748</v>
       </c>
       <c r="G6" t="n">
         <v>0.7336</v>
@@ -922,13 +922,13 @@
         <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4539</v>
+        <v>-0.3614</v>
       </c>
       <c r="T6" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3854</v>
+        <v>-0.2929</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4569</v>
+        <v>-1.2228</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8505</v>
+        <v>-0.4616</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.3073</v>
+        <v>-0.7612</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9954</v>
+        <v>-1.6882</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.503</v>
+        <v>-0.5264</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5077</v>
+        <v>-1.1618</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8058</v>
+        <v>-0.535</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5052</v>
+        <v>0.438</v>
       </c>
       <c r="L7" t="n">
-        <v>3.311</v>
+        <v>-0.9729</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8012</v>
+        <v>-1.1532</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9978</v>
+        <v>-0.9643</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8033</v>
+        <v>-0.1889</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1714</v>
+        <v>-0.1872</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0853</v>
+        <v>0.0733</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2567</v>
+        <v>-0.2605</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.3729</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.5029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6643</v>
+        <v>-1.3529</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9339</v>
+        <v>0.2873</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7304</v>
+        <v>-1.6402</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6882</v>
+        <v>-0.973</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5264</v>
+        <v>-1.4599</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1618</v>
+        <v>0.4869</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.535</v>
+        <v>0.4447</v>
       </c>
       <c r="K8" t="n">
-        <v>0.438</v>
+        <v>-0.3801</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9729</v>
+        <v>0.8248</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1532</v>
+        <v>-1.4178</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9643</v>
+        <v>-1.0799</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1889</v>
+        <v>-0.3379</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6286</v>
+        <v>-0.1199</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.399</v>
+        <v>-0.1574</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2297</v>
+        <v>0.0375</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0294</v>
+        <v>-1.71</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2967</v>
+        <v>2.7207</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7326</v>
+        <v>-4.4306</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.973</v>
+        <v>-0.9954</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4599</v>
+        <v>-2.503</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4869</v>
+        <v>1.5077</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4447</v>
+        <v>1.8058</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3801</v>
+        <v>-1.5052</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8248</v>
+        <v>3.311</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4178</v>
+        <v>-2.8012</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0799</v>
+        <v>-0.9978</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3379</v>
+        <v>-1.8033</v>
       </c>
       <c r="P9" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7964</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.2151</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0549</v>
+        <v>0.1334</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>-2.3729</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>-3.5029</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8108</v>
+        <v>-1.8937</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.813</v>
+        <v>-1.1424</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9978</v>
+        <v>-0.7512</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5247</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8256</v>
+        <v>-0.9085</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3014</v>
+        <v>-0.6309</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5242</v>
+        <v>-0.2776</v>
       </c>
       <c r="V10" t="n">
         <v>-0.113</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0403</v>
+        <v>-2.5295</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8357</v>
+        <v>-2.1399</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2046</v>
+        <v>-0.3896</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2709</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5944</v>
+        <v>-0.0835</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6044</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0101</v>
+        <v>-0.1749</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1842</v>
+        <v>-3.2583</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5102</v>
+        <v>-0.5535</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.674</v>
+        <v>-2.7048</v>
       </c>
       <c r="G12" t="n">
         <v>-3.104</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.512</v>
+        <v>-0.5861</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3389</v>
+        <v>-0.3821</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1732</v>
+        <v>-0.204</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8732</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.587299999999999</v>
+        <v>-6.559800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>9.0937</v>
+        <v>10.1211</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.6807</v>
+        <v>-16.6808</v>
       </c>
       <c r="G13" t="n">
         <v>-8.287500000000001</v>
@@ -1441,7 +1441,7 @@
         <v>0.7451</v>
       </c>
       <c r="J13" t="n">
-        <v>8.981999999999999</v>
+        <v>8.982000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>1.3558</v>
@@ -1468,13 +1468,13 @@
         <v>11.9628</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.8875</v>
+        <v>-2.86</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1389</v>
+        <v>-1.1115</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7486</v>
+        <v>-1.7485</v>
       </c>
       <c r="V13" t="n">
         <v>1.325200000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3748</v>
+        <v>5.8449</v>
       </c>
       <c r="E14" t="n">
-        <v>9.1355</v>
+        <v>9.359</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7608</v>
+        <v>-3.5142</v>
       </c>
       <c r="G14" t="n">
         <v>1.7894</v>
@@ -1546,13 +1546,13 @@
         <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1079</v>
+        <v>0.578</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2896</v>
+        <v>0.5131</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1817</v>
+        <v>0.0649</v>
       </c>
       <c r="V14" t="n">
         <v>2.8249</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>D. RADONCIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6452</v>
+        <v>2.8285</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5236</v>
+        <v>2.1808</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1216</v>
+        <v>0.6478</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2288</v>
+        <v>2.9531</v>
       </c>
       <c r="H15" t="n">
-        <v>0.879</v>
+        <v>0.9275</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3498</v>
+        <v>2.0256</v>
       </c>
       <c r="J15" t="n">
-        <v>2.186</v>
+        <v>3.8928</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8823</v>
+        <v>1.4449</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3037</v>
+        <v>2.448</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.9397</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0033</v>
+        <v>-0.5173</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9539</v>
+        <v>-0.4224</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4609</v>
+        <v>-0.167</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0347</v>
+        <v>-0.4494</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4262</v>
+        <v>0.2824</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. RADONCIC</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.456</v>
+        <v>2.816</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9573</v>
+        <v>2.1612</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4987</v>
+        <v>0.6548</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9531</v>
+        <v>2.378</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9275</v>
+        <v>1.6393</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0256</v>
+        <v>0.7387</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8928</v>
+        <v>1.8824</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4449</v>
+        <v>1.4417</v>
       </c>
       <c r="L16" t="n">
-        <v>2.448</v>
+        <v>0.4407</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9397</v>
+        <v>0.4956</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5173</v>
+        <v>0.1976</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4224</v>
+        <v>0.298</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5396</v>
+        <v>0.2205</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.2788</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1334</v>
+        <v>-0.0583</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4191</v>
+        <v>2.2174</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8259</v>
+        <v>2.1883</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.0291</v>
       </c>
       <c r="G17" t="n">
-        <v>2.378</v>
+        <v>1.2288</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6393</v>
+        <v>0.879</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7387</v>
+        <v>0.3498</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8824</v>
+        <v>2.186</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4417</v>
+        <v>0.8823</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4407</v>
+        <v>1.3037</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4956</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1976</v>
+        <v>-0.0033</v>
       </c>
       <c r="O17" t="n">
-        <v>0.298</v>
+        <v>-0.9539</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1764</v>
+        <v>1.0332</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0565</v>
+        <v>0.6994</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1199</v>
+        <v>0.3338</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1761</v>
+        <v>1.8631</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9837</v>
+        <v>2.0045</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8076</v>
+        <v>-0.1414</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8658</v>
+        <v>2.3617</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7312</v>
+        <v>1.5967</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8653999999999999</v>
+        <v>0.765</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1856</v>
+        <v>3.7994</v>
       </c>
       <c r="K18" t="n">
-        <v>3.0326</v>
+        <v>2.2296</v>
       </c>
       <c r="L18" t="n">
-        <v>0.153</v>
+        <v>1.5698</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3197</v>
+        <v>-1.4377</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3013</v>
+        <v>-0.6328</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0184</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P18" t="n">
         <v>-0.2175</v>
@@ -1858,28 +1858,28 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.853</v>
+        <v>0.0886</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1032</v>
+        <v>-0.1202</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2502</v>
+        <v>0.2088</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3252</v>
+        <v>-0.3698</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1014</v>
+        <v>0.4811</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6692</v>
+        <v>2.2014</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5678</v>
+        <v>-1.7202</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3617</v>
+        <v>1.8658</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5967</v>
+        <v>2.7312</v>
       </c>
       <c r="I19" t="n">
-        <v>0.765</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7994</v>
+        <v>3.1856</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2296</v>
+        <v>3.0326</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5698</v>
+        <v>0.153</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4377</v>
+        <v>-1.3197</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6328</v>
+        <v>-0.3013</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-1.0184</v>
       </c>
       <c r="P19" t="n">
         <v>-0.2175</v>
@@ -1936,28 +1936,28 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6731</v>
+        <v>0.158</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4554</v>
+        <v>0.3209</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2176</v>
+        <v>-0.1628</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3698</v>
+        <v>-1.3252</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4805</v>
+        <v>-0.2039</v>
       </c>
       <c r="E20" t="n">
-        <v>1.291</v>
+        <v>-0.416</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8105</v>
+        <v>0.2122</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1378</v>
+        <v>-0.1194</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1522</v>
+        <v>-0.5505</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0143</v>
+        <v>0.4311</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6368</v>
+        <v>-0.4461</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0333</v>
+        <v>-0.5991</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6702</v>
+        <v>0.153</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7747000000000001</v>
+        <v>0.3267</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1188</v>
+        <v>0.0486</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6558</v>
+        <v>0.2781</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3361</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6992</v>
+        <v>0.03</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6369</v>
+        <v>0.5582</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>-1.3252</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2682</v>
+        <v>-0.5253</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6395</v>
+        <v>0.2851</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3714</v>
+        <v>-0.8105</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1194</v>
+        <v>-0.1378</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5505</v>
+        <v>-0.1522</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4311</v>
+        <v>0.0143</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4461</v>
+        <v>0.6368</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5991</v>
+        <v>-0.0333</v>
       </c>
       <c r="L21" t="n">
-        <v>0.153</v>
+        <v>0.6702</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3267</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0486</v>
+        <v>-0.1188</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2781</v>
+        <v>-0.6558</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5239</v>
+        <v>1.3303</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1935</v>
+        <v>0.6934</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7174</v>
+        <v>0.6369</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>-1.3252</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8216</v>
+        <v>-0.7921</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0844</v>
+        <v>-0.4197</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7372</v>
+        <v>-0.3724</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1607</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0994</v>
+        <v>0.1289</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2091</v>
+        <v>-0.1262</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1097</v>
+        <v>0.2551</v>
       </c>
       <c r="V22" t="n">
         <v>0.3698</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6088</v>
+        <v>-1.1232</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5808</v>
+        <v>-0.9102</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.028</v>
+        <v>-0.213</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9219000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4694</v>
+        <v>0.0162</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8784</v>
+        <v>-0.2079</v>
       </c>
       <c r="U23" t="n">
-        <v>0.409</v>
+        <v>0.2241</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3672</v>
+        <v>-5.0743</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4006</v>
+        <v>-1.9536</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9666</v>
+        <v>-3.1207</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9494</v>
@@ -2326,13 +2326,13 @@
         <v>0.2175</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3647</v>
+        <v>0.6576</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3305</v>
+        <v>0.1166</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6952</v>
+        <v>0.5411</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8249</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.587299999999997</v>
+        <v>8.3322</v>
       </c>
       <c r="E25" t="n">
-        <v>16.6809</v>
+        <v>16.6808</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.0936</v>
+        <v>-8.3485</v>
       </c>
       <c r="G25" t="n">
         <v>8.287599999999998</v>
@@ -2404,13 +2404,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>3.887400000000001</v>
+        <v>4.632499999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.7486</v>
+        <v>1.7485</v>
       </c>
       <c r="U25" t="n">
-        <v>2.139</v>
+        <v>2.8842</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3252</v>
